--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>113396051</v>
       </c>
       <c r="B6" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>113396049</v>
       </c>
       <c r="B7" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>113396051</v>
       </c>
       <c r="B6" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>113396049</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113396051</v>
+        <v>113396049</v>
       </c>
       <c r="B6" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1209,24 +1209,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577986</v>
+        <v>577897</v>
       </c>
       <c r="R6" t="n">
-        <v>6966394</v>
+        <v>6966411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1251,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113396049</v>
+        <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>56785</v>
+        <v>56773</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,16 +1298,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1319,16 +1316,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577897</v>
+        <v>577986</v>
       </c>
       <c r="R7" t="n">
-        <v>6966411</v>
+        <v>6966394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,11 +1366,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113396049</v>
+        <v>113396051</v>
       </c>
       <c r="B6" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1209,16 +1209,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577897</v>
+        <v>577986</v>
       </c>
       <c r="R6" t="n">
-        <v>6966411</v>
+        <v>6966394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113396051</v>
+        <v>113396049</v>
       </c>
       <c r="B7" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,16 +1301,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1316,24 +1319,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577986</v>
+        <v>577897</v>
       </c>
       <c r="R7" t="n">
-        <v>6966394</v>
+        <v>6966411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,6 +1361,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>113396051</v>
       </c>
       <c r="B6" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>113396049</v>
       </c>
       <c r="B7" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>113396051</v>
       </c>
       <c r="B6" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>113396049</v>
       </c>
       <c r="B7" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113396051</v>
+        <v>113396049</v>
       </c>
       <c r="B6" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1209,24 +1209,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577986</v>
+        <v>577897</v>
       </c>
       <c r="R6" t="n">
-        <v>6966394</v>
+        <v>6966411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1251,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113396049</v>
+        <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,16 +1298,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1319,16 +1316,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577897</v>
+        <v>577986</v>
       </c>
       <c r="R7" t="n">
-        <v>6966411</v>
+        <v>6966394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,11 +1366,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17266200</v>
+        <v>17266207</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577940.2988796626</v>
+        <v>577940</v>
       </c>
       <c r="R2" t="n">
-        <v>6966387.625681015</v>
+        <v>6966388</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -752,19 +747,9 @@
           <t>2014-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17266207</v>
+        <v>17266205</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577940.2988796626</v>
+        <v>577940</v>
       </c>
       <c r="R3" t="n">
-        <v>6966387.625681015</v>
+        <v>6966388</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +857,9 @@
           <t>2014-08-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,12 +898,7 @@
         <v>17266214</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577940.2988796626</v>
+        <v>577940</v>
       </c>
       <c r="R4" t="n">
-        <v>6966387.625681015</v>
+        <v>6966388</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1002,19 +967,9 @@
           <t>2014-08-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17266205</v>
+        <v>113396049</v>
       </c>
       <c r="B5" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,41 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäckemyran, Mpd</t>
+          <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577940.2988796626</v>
+        <v>577897</v>
       </c>
       <c r="R5" t="n">
-        <v>6966387.625681015</v>
+        <v>6966411</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,44 +1091,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113396049</v>
+        <v>120348748</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1211,14 +1138,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkstensjö, Mpd</t>
+          <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577897</v>
+        <v>577838</v>
       </c>
       <c r="R6" t="n">
-        <v>6966411</v>
+        <v>6966437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,12 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,12 +1212,7 @@
         <v>113396051</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 48777-2023 artfynd.xlsx
+++ b/artfynd/A 48777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17266207</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17266205</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17266214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396049</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,8 +1341,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>